--- a/中医_情志规则库.xlsx
+++ b/中医_情志规则库.xlsx
@@ -55,106 +55,106 @@
     <t>怒</t>
   </si>
   <si>
-    <t>烦躁、生气、发火、憋屈、不公平</t>
+    <t>烦躁,生气,发火,憋屈,不公平</t>
   </si>
   <si>
     <t>肝</t>
   </si>
   <si>
-    <t>肝气郁结、肝火上炎</t>
+    <t>"肝气郁结","肝火上炎"</t>
   </si>
   <si>
     <t>悲 (悲胜怒)</t>
   </si>
   <si>
-    <t>“嘘”字诀呼吸6次、远眺绿色植物</t>
-  </si>
-  <si>
-    <t>羽调音乐、菊花茶、按揉太冲穴</t>
+    <t>"“嘘”字诀呼吸6次","远眺绿色植物"</t>
+  </si>
+  <si>
+    <t>"羽调音乐","菊花茶","按揉太冲穴"</t>
   </si>
   <si>
     <t>思</t>
   </si>
   <si>
-    <t>忧虑、反复想、纠结、放不下、担心</t>
+    <t>"忧虑","反复想","纠结","放不下","担心"</t>
   </si>
   <si>
     <t>脾</t>
   </si>
   <si>
-    <t>思伤脾、气机郁结</t>
+    <t>"思伤脾","气机郁结"</t>
   </si>
   <si>
     <t>怒 (怒胜思)</t>
   </si>
   <si>
-    <t>竞技性运动（乒乓球）、八段锦</t>
-  </si>
-  <si>
-    <t>角调音乐、山药粥、按揉足三里</t>
+    <t>"竞技性运动（乒乓球）","八段锦"</t>
+  </si>
+  <si>
+    <t>"角调音乐","山药粥","按揉足三里"</t>
   </si>
   <si>
     <t>悲 (忧)</t>
   </si>
   <si>
-    <t>悲伤、失落、无望、孤独、难过</t>
+    <t>"悲伤","失落","无望","孤独","难过"</t>
   </si>
   <si>
     <t>肺</t>
   </si>
   <si>
-    <t>悲伤肺、肺气不足</t>
+    <t>"悲伤肺","肺气不足"</t>
   </si>
   <si>
     <t>喜 (喜胜悲)</t>
   </si>
   <si>
-    <t>观看喜剧、回忆快乐往事、晒太阳</t>
-  </si>
-  <si>
-    <t>徵调音乐、百合莲子汤、轻拍膻中穴</t>
+    <t>"观看喜剧","回忆快乐往事","晒太阳"</t>
+  </si>
+  <si>
+    <t>"徵调音乐","百合莲子汤","轻拍膻中穴"</t>
   </si>
   <si>
     <t>恐</t>
   </si>
   <si>
-    <t>害怕、不安、恐慌、担心灾难</t>
+    <t>"害怕","不安","恐慌","担心灾难"</t>
   </si>
   <si>
     <t>肾</t>
   </si>
   <si>
-    <t>恐伤肾、肾气不固</t>
+    <t>"恐伤肾","肾气不固"</t>
   </si>
   <si>
     <t>思 (思胜恐)</t>
   </si>
   <si>
-    <t>正念 grounding练习、制定计划</t>
-  </si>
-  <si>
-    <t>宫调音乐、黑豆核桃粥、搓揉涌泉穴</t>
+    <t>"正念 grounding练习","制定计划"</t>
+  </si>
+  <si>
+    <t>"宫调音乐","黑豆核桃粥","搓揉涌泉穴"</t>
   </si>
   <si>
     <t>喜</t>
   </si>
   <si>
-    <t>过度兴奋、狂喜、大喜</t>
+    <t>"过度兴奋","狂喜","大喜"</t>
   </si>
   <si>
     <t>心</t>
   </si>
   <si>
-    <t>喜伤心、心神涣散</t>
+    <t>"喜伤心","心神涣散"</t>
   </si>
   <si>
     <t>恐 (恐胜喜)</t>
   </si>
   <si>
-    <t>静坐、阅读严肃内容、冷水洗脸</t>
-  </si>
-  <si>
-    <t>商调音乐、莲子心茶、按揉神门穴</t>
+    <t>"静坐","阅读严肃内容","冷水洗脸"</t>
+  </si>
+  <si>
+    <t>"商调音乐","莲子心茶","按揉神门穴"</t>
   </si>
 </sst>
 </file>
